--- a/ui_runner/templates/graded_analysis_tabs_2026-06-02.xlsx
+++ b/ui_runner/templates/graded_analysis_tabs_2026-06-02.xlsx
@@ -471,16 +471,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G2" t="n">
-        <v>61.3</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3">
@@ -500,16 +500,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="E3" t="n">
         <v>117</v>
       </c>
       <c r="F3" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="G3" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="4">
@@ -529,16 +529,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E4" t="n">
         <v>26</v>
       </c>
       <c r="F4" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G4" t="n">
-        <v>49.1</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="5">
@@ -558,16 +558,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="E5" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F5" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G5" t="n">
-        <v>54.2</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="6">
@@ -587,16 +587,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E6" t="n">
         <v>23</v>
       </c>
       <c r="F6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G6" t="n">
-        <v>48.9</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="7">
@@ -645,16 +645,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>474</v>
+        <v>214</v>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>98</v>
       </c>
       <c r="F8" t="n">
-        <v>289</v>
+        <v>116</v>
       </c>
       <c r="G8" t="n">
-        <v>39</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="9">
@@ -674,16 +674,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>57.9</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10">
@@ -732,16 +732,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1079</v>
+        <v>1128</v>
       </c>
       <c r="E11" t="n">
-        <v>708</v>
+        <v>737</v>
       </c>
       <c r="F11" t="n">
-        <v>371</v>
+        <v>391</v>
       </c>
       <c r="G11" t="n">
-        <v>65.59999999999999</v>
+        <v>65.3</v>
       </c>
     </row>
     <row r="12">
@@ -761,16 +761,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="E12" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F12" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G12" t="n">
-        <v>63.3</v>
+        <v>62.8</v>
       </c>
     </row>
     <row r="13">
@@ -790,16 +790,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E13" t="n">
         <v>47</v>
       </c>
       <c r="F13" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G13" t="n">
-        <v>27.3</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="14">
@@ -819,16 +819,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="E14" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="F14" t="n">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="G14" t="n">
-        <v>29.5</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="15">
@@ -848,16 +848,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>577</v>
+        <v>589</v>
       </c>
       <c r="E15" t="n">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="F15" t="n">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="G15" t="n">
-        <v>26.2</v>
+        <v>26.3</v>
       </c>
     </row>
     <row r="16">
@@ -877,16 +877,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="E16" t="n">
         <v>43</v>
       </c>
       <c r="F16" t="n">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="G16" t="n">
-        <v>20.4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -906,16 +906,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>4291</v>
+        <v>4510</v>
       </c>
       <c r="E17" t="n">
-        <v>960</v>
+        <v>1006</v>
       </c>
       <c r="F17" t="n">
-        <v>3331</v>
+        <v>3504</v>
       </c>
       <c r="G17" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
     </row>
   </sheetData>
@@ -1163,10 +1163,10 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>34</v>
+        <v>48.1</v>
       </c>
       <c r="Y2" t="n">
-        <v>312</v>
+        <v>27</v>
       </c>
       <c r="Z2" t="n">
         <v>69.59999999999999</v>
@@ -1183,11 +1183,8 @@
       <c r="AE2" t="n">
         <v>0</v>
       </c>
-      <c r="AF2" t="n">
-        <v>46.7</v>
-      </c>
       <c r="AG2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -1522,82 +1519,82 @@
         <v>165</v>
       </c>
       <c r="D7" t="n">
-        <v>65.59999999999999</v>
+        <v>65.3</v>
       </c>
       <c r="E7" t="n">
-        <v>1079</v>
+        <v>1128</v>
       </c>
       <c r="F7" t="n">
-        <v>63.3</v>
+        <v>62.8</v>
       </c>
       <c r="G7" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="H7" t="n">
-        <v>27.3</v>
+        <v>27.2</v>
       </c>
       <c r="I7" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="J7" t="n">
-        <v>29.5</v>
+        <v>29.6</v>
       </c>
       <c r="K7" t="n">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="L7" t="n">
-        <v>26.2</v>
+        <v>26.3</v>
       </c>
       <c r="M7" t="n">
-        <v>577</v>
+        <v>589</v>
       </c>
       <c r="N7" t="n">
-        <v>20.4</v>
+        <v>20</v>
       </c>
       <c r="O7" t="n">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="P7" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>4291</v>
+        <v>4510</v>
       </c>
       <c r="R7" t="n">
-        <v>61.3</v>
+        <v>61</v>
       </c>
       <c r="S7" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="T7" t="n">
-        <v>49.1</v>
+        <v>45.6</v>
       </c>
       <c r="U7" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="V7" t="n">
-        <v>48.9</v>
+        <v>47.9</v>
       </c>
       <c r="W7" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="X7" t="n">
-        <v>39</v>
+        <v>45.8</v>
       </c>
       <c r="Y7" t="n">
-        <v>474</v>
+        <v>214</v>
       </c>
       <c r="Z7" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="AA7" t="n">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="AB7" t="n">
-        <v>54.2</v>
+        <v>54.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="AD7" t="n">
         <v>25</v>
@@ -1606,10 +1603,10 @@
         <v>12</v>
       </c>
       <c r="AF7" t="n">
-        <v>57.9</v>
+        <v>100</v>
       </c>
       <c r="AG7" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
